--- a/poker/resources/sample/poker/PokerPool.xlsx
+++ b/poker/resources/sample/poker/PokerPool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project2\poker\resources\sample\poker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59DFC0F-AF64-48B9-AB18-ED66029F3FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825309A7-91EA-4E4A-858A-FD7B23E1B41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="PokerPool" sheetId="22" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PokerPool!$B$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PokerPool!$B$1:$G$160</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,6 +106,9 @@
     <t>suitNum</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Diamond</t>
   </si>
   <si>
@@ -134,9 +137,6 @@
   </si>
   <si>
     <t>无</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>2最大</t>
@@ -176,7 +176,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,12 +214,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -282,7 +276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -299,13 +293,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -600,7 +591,7 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.125" style="1" customWidth="1"/>
@@ -615,7 +606,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -638,7 +629,7 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -658,7 +649,7 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -682,19 +673,19 @@
         <v>100001</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -705,19 +696,19 @@
         <v>100001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -728,19 +719,19 @@
         <v>100001</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -751,19 +742,19 @@
         <v>100001</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -773,20 +764,20 @@
       <c r="B9" s="1">
         <v>100001</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -796,20 +787,20 @@
       <c r="B10" s="1">
         <v>100001</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -819,20 +810,20 @@
       <c r="B11" s="1">
         <v>100001</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1">
         <v>3</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -842,20 +833,20 @@
       <c r="B12" s="1">
         <v>100001</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -865,20 +856,20 @@
       <c r="B13" s="1">
         <v>100001</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -888,20 +879,20 @@
       <c r="B14" s="1">
         <v>100001</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -911,20 +902,20 @@
       <c r="B15" s="1">
         <v>100001</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -934,20 +925,20 @@
       <c r="B16" s="1">
         <v>100001</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -957,20 +948,20 @@
       <c r="B17" s="1">
         <v>100001</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -980,20 +971,20 @@
       <c r="B18" s="1">
         <v>100001</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="1">
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1003,20 +994,20 @@
       <c r="B19" s="1">
         <v>100001</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1026,20 +1017,20 @@
       <c r="B20" s="1">
         <v>100001</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1049,20 +1040,20 @@
       <c r="B21" s="1">
         <v>100001</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1072,20 +1063,20 @@
       <c r="B22" s="1">
         <v>100001</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1095,20 +1086,20 @@
       <c r="B23" s="1">
         <v>100001</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1118,20 +1109,20 @@
       <c r="B24" s="1">
         <v>100001</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1141,20 +1132,20 @@
       <c r="B25" s="1">
         <v>100001</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1164,20 +1155,20 @@
       <c r="B26" s="1">
         <v>100001</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="1">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1187,20 +1178,20 @@
       <c r="B27" s="1">
         <v>100001</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="1">
         <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1">
         <v>3</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1210,20 +1201,20 @@
       <c r="B28" s="1">
         <v>100001</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="1">
         <v>6</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1233,20 +1224,20 @@
       <c r="B29" s="1">
         <v>100001</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="1">
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1256,20 +1247,20 @@
       <c r="B30" s="1">
         <v>100001</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="1">
         <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1279,20 +1270,20 @@
       <c r="B31" s="1">
         <v>100001</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="1">
         <v>7</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1302,20 +1293,20 @@
       <c r="B32" s="1">
         <v>100001</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D32" s="1">
         <v>7</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1325,20 +1316,20 @@
       <c r="B33" s="1">
         <v>100001</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="1">
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1348,20 +1339,20 @@
       <c r="B34" s="1">
         <v>100001</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1371,20 +1362,20 @@
       <c r="B35" s="1">
         <v>100001</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="1">
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1394,20 +1385,20 @@
       <c r="B36" s="1">
         <v>100001</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="1">
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" s="1">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1417,20 +1408,20 @@
       <c r="B37" s="1">
         <v>100001</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D37" s="1">
         <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1440,20 +1431,20 @@
       <c r="B38" s="1">
         <v>100001</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D38" s="1">
         <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1">
+        <v>2</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1463,20 +1454,20 @@
       <c r="B39" s="1">
         <v>100001</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D39" s="1">
         <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1486,20 +1477,20 @@
       <c r="B40" s="1">
         <v>100001</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D40" s="1">
         <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1">
         <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1509,20 +1500,20 @@
       <c r="B41" s="1">
         <v>100001</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="1">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1532,20 +1523,20 @@
       <c r="B42" s="1">
         <v>100001</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="1">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1555,20 +1546,20 @@
       <c r="B43" s="1">
         <v>100001</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D43" s="1">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1">
         <v>3</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1578,20 +1569,20 @@
       <c r="B44" s="1">
         <v>100001</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="1">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44" s="1">
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1601,20 +1592,20 @@
       <c r="B45" s="1">
         <v>100001</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>19</v>
+      <c r="C45" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D45" s="1">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1624,20 +1615,20 @@
       <c r="B46" s="1">
         <v>100001</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>19</v>
+      <c r="C46" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D46" s="1">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1">
         <v>2</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1647,20 +1638,20 @@
       <c r="B47" s="1">
         <v>100001</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>19</v>
+      <c r="C47" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D47" s="1">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1670,20 +1661,20 @@
       <c r="B48" s="1">
         <v>100001</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>19</v>
+      <c r="C48" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D48" s="1">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" s="1">
         <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1693,20 +1684,20 @@
       <c r="B49" s="1">
         <v>100001</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>21</v>
+      <c r="C49" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D49" s="1">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1716,20 +1707,20 @@
       <c r="B50" s="1">
         <v>100001</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>21</v>
+      <c r="C50" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D50" s="1">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1">
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1739,20 +1730,20 @@
       <c r="B51" s="1">
         <v>100001</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>21</v>
+      <c r="C51" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D51" s="1">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1">
         <v>3</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1762,20 +1753,20 @@
       <c r="B52" s="1">
         <v>100001</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>21</v>
+      <c r="C52" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D52" s="1">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F52" s="1">
         <v>4</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1785,20 +1776,20 @@
       <c r="B53" s="1">
         <v>100001</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>22</v>
+      <c r="C53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D53" s="1">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1808,20 +1799,20 @@
       <c r="B54" s="1">
         <v>100001</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>22</v>
+      <c r="C54" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D54" s="1">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1831,20 +1822,20 @@
       <c r="B55" s="1">
         <v>100001</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>22</v>
+      <c r="C55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D55" s="1">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1854,20 +1845,20 @@
       <c r="B56" s="1">
         <v>100001</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>22</v>
+      <c r="C56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D56" s="1">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1">
         <v>4</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1884,13 +1875,13 @@
         <v>2</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1907,13 +1898,13 @@
         <v>2</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F58" s="1">
         <v>2</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1930,13 +1921,13 @@
         <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1953,13 +1944,13 @@
         <v>2</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1">
         <v>4</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1976,13 +1967,13 @@
         <v>3</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1999,13 +1990,13 @@
         <v>3</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2022,13 +2013,13 @@
         <v>3</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2045,13 +2036,13 @@
         <v>3</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" s="1">
         <v>4</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2068,13 +2059,13 @@
         <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2091,13 +2082,13 @@
         <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F66" s="1">
         <v>2</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2107,20 +2098,20 @@
       <c r="B67" s="1">
         <v>100002</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1">
         <v>3</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2130,20 +2121,20 @@
       <c r="B68" s="1">
         <v>100002</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F68" s="1">
         <v>4</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2153,20 +2144,20 @@
       <c r="B69" s="1">
         <v>100002</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D69" s="1">
         <v>5</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2176,20 +2167,20 @@
       <c r="B70" s="1">
         <v>100002</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1">
         <v>2</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2199,20 +2190,20 @@
       <c r="B71" s="1">
         <v>100002</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1">
         <v>3</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2222,20 +2213,20 @@
       <c r="B72" s="1">
         <v>100002</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F72" s="1">
         <v>4</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2245,20 +2236,20 @@
       <c r="B73" s="1">
         <v>100002</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D73" s="1">
         <v>6</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2268,20 +2259,20 @@
       <c r="B74" s="1">
         <v>100002</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D74" s="1">
         <v>6</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2291,20 +2282,20 @@
       <c r="B75" s="1">
         <v>100002</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D75" s="1">
         <v>6</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1">
         <v>3</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2314,20 +2305,20 @@
       <c r="B76" s="1">
         <v>100002</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D76" s="1">
         <v>6</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F76" s="1">
         <v>4</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2337,20 +2328,20 @@
       <c r="B77" s="1">
         <v>100002</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D77" s="1">
         <v>7</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2360,20 +2351,20 @@
       <c r="B78" s="1">
         <v>100002</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D78" s="1">
         <v>7</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2383,20 +2374,20 @@
       <c r="B79" s="1">
         <v>100002</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D79" s="1">
         <v>7</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1">
         <v>3</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2406,20 +2397,20 @@
       <c r="B80" s="1">
         <v>100002</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D80" s="1">
         <v>7</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F80" s="1">
         <v>4</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2429,20 +2420,20 @@
       <c r="B81" s="1">
         <v>100002</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D81" s="1">
         <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1">
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2452,20 +2443,20 @@
       <c r="B82" s="1">
         <v>100002</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D82" s="1">
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1">
         <v>2</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2475,20 +2466,20 @@
       <c r="B83" s="1">
         <v>100002</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D83" s="1">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1">
         <v>3</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2498,20 +2489,20 @@
       <c r="B84" s="1">
         <v>100002</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D84" s="1">
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F84" s="1">
         <v>4</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2521,20 +2512,20 @@
       <c r="B85" s="1">
         <v>100002</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="1">
         <v>9</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2544,20 +2535,20 @@
       <c r="B86" s="1">
         <v>100002</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="1">
         <v>9</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1">
         <v>2</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2567,20 +2558,20 @@
       <c r="B87" s="1">
         <v>100002</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D87" s="1">
         <v>9</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1">
         <v>3</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2590,20 +2581,20 @@
       <c r="B88" s="1">
         <v>100002</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D88" s="1">
         <v>9</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F88" s="1">
         <v>4</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2613,20 +2604,20 @@
       <c r="B89" s="1">
         <v>100002</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="1">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2636,20 +2627,20 @@
       <c r="B90" s="1">
         <v>100002</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D90" s="1">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2659,20 +2650,20 @@
       <c r="B91" s="1">
         <v>100002</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D91" s="1">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2682,20 +2673,20 @@
       <c r="B92" s="1">
         <v>100002</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D92" s="1">
         <v>10</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F92" s="1">
         <v>4</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2705,20 +2696,20 @@
       <c r="B93" s="1">
         <v>100002</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>19</v>
+      <c r="C93" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D93" s="1">
         <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2728,20 +2719,20 @@
       <c r="B94" s="1">
         <v>100002</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>19</v>
+      <c r="C94" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D94" s="1">
         <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1">
         <v>2</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2751,20 +2742,20 @@
       <c r="B95" s="1">
         <v>100002</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>19</v>
+      <c r="C95" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D95" s="1">
         <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2774,20 +2765,20 @@
       <c r="B96" s="1">
         <v>100002</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>19</v>
+      <c r="C96" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D96" s="1">
         <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1">
         <v>4</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2797,20 +2788,20 @@
       <c r="B97" s="1">
         <v>100002</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>21</v>
+      <c r="C97" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D97" s="1">
         <v>12</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2820,20 +2811,20 @@
       <c r="B98" s="1">
         <v>100002</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>21</v>
+      <c r="C98" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D98" s="1">
         <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F98" s="1">
         <v>2</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2843,20 +2834,20 @@
       <c r="B99" s="1">
         <v>100002</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>21</v>
+      <c r="C99" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D99" s="1">
         <v>12</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2866,20 +2857,20 @@
       <c r="B100" s="1">
         <v>100002</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>21</v>
+      <c r="C100" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D100" s="1">
         <v>12</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F100" s="1">
         <v>4</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2889,20 +2880,20 @@
       <c r="B101" s="1">
         <v>100002</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>22</v>
+      <c r="C101" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D101" s="1">
         <v>13</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2912,20 +2903,20 @@
       <c r="B102" s="1">
         <v>100002</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>22</v>
+      <c r="C102" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D102" s="1">
         <v>13</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F102" s="1">
         <v>2</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -2935,20 +2926,20 @@
       <c r="B103" s="1">
         <v>100002</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>22</v>
+      <c r="C103" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D103" s="1">
         <v>13</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1">
         <v>3</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -2958,20 +2949,20 @@
       <c r="B104" s="1">
         <v>100002</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>22</v>
+      <c r="C104" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D104" s="1">
         <v>13</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F104" s="1">
         <v>4</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -2981,20 +2972,20 @@
       <c r="B105" s="1">
         <v>100002</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>24</v>
+      <c r="C105" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D105" s="1">
         <v>14</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3004,20 +2995,20 @@
       <c r="B106" s="1">
         <v>100002</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>24</v>
+      <c r="C106" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D106" s="1">
         <v>14</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1">
         <v>2</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3027,20 +3018,20 @@
       <c r="B107" s="1">
         <v>100002</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>24</v>
+      <c r="C107" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D107" s="1">
         <v>14</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1">
         <v>3</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3050,20 +3041,20 @@
       <c r="B108" s="1">
         <v>100002</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>24</v>
+      <c r="C108" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D108" s="1">
         <v>14</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F108" s="1">
         <v>4</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3073,14 +3064,14 @@
       <c r="B109" s="1">
         <v>100003</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D109" s="1">
         <v>15</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1">
         <v>2</v>
@@ -3096,14 +3087,14 @@
       <c r="B110" s="1">
         <v>100003</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D110" s="1">
         <v>15</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1">
         <v>3</v>
@@ -3119,14 +3110,14 @@
       <c r="B111" s="1">
         <v>100003</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D111" s="1">
         <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -3142,14 +3133,14 @@
       <c r="B112" s="1">
         <v>100003</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D112" s="1">
         <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F112" s="1">
         <v>4</v>
@@ -3165,20 +3156,20 @@
       <c r="B113" s="1">
         <v>100003</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1">
         <v>2</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3188,20 +3179,20 @@
       <c r="B114" s="1">
         <v>100003</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1">
         <v>3</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3211,20 +3202,20 @@
       <c r="B115" s="1">
         <v>100003</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3234,20 +3225,20 @@
       <c r="B116" s="1">
         <v>100003</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1">
         <v>4</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3257,20 +3248,20 @@
       <c r="B117" s="1">
         <v>100003</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D117" s="1">
         <v>4</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1">
         <v>2</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3280,20 +3271,20 @@
       <c r="B118" s="1">
         <v>100003</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="1">
         <v>4</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1">
         <v>3</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3303,20 +3294,20 @@
       <c r="B119" s="1">
         <v>100003</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="1">
         <v>4</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3326,20 +3317,20 @@
       <c r="B120" s="1">
         <v>100003</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="1">
         <v>4</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1">
         <v>4</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3349,20 +3340,20 @@
       <c r="B121" s="1">
         <v>100003</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D121" s="1">
         <v>5</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1">
         <v>2</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3372,20 +3363,20 @@
       <c r="B122" s="1">
         <v>100003</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D122" s="1">
         <v>5</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1">
         <v>3</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3395,20 +3386,20 @@
       <c r="B123" s="1">
         <v>100003</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D123" s="1">
         <v>5</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3418,20 +3409,20 @@
       <c r="B124" s="1">
         <v>100003</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D124" s="1">
         <v>5</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1">
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3441,20 +3432,20 @@
       <c r="B125" s="1">
         <v>100003</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D125" s="1">
         <v>6</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1">
         <v>2</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3464,20 +3455,20 @@
       <c r="B126" s="1">
         <v>100003</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D126" s="1">
         <v>6</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1">
         <v>3</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3487,20 +3478,20 @@
       <c r="B127" s="1">
         <v>100003</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C127" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D127" s="1">
         <v>6</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3510,20 +3501,20 @@
       <c r="B128" s="1">
         <v>100003</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C128" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D128" s="1">
         <v>6</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1">
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3533,20 +3524,20 @@
       <c r="B129" s="1">
         <v>100003</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D129" s="1">
         <v>7</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1">
         <v>2</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3556,20 +3547,20 @@
       <c r="B130" s="1">
         <v>100003</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C130" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D130" s="1">
         <v>7</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1">
         <v>3</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3579,20 +3570,20 @@
       <c r="B131" s="1">
         <v>100003</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C131" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D131" s="1">
         <v>7</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3602,20 +3593,20 @@
       <c r="B132" s="1">
         <v>100003</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D132" s="1">
         <v>7</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F132" s="1">
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3625,20 +3616,20 @@
       <c r="B133" s="1">
         <v>100003</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D133" s="1">
         <v>8</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1">
         <v>2</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3648,20 +3639,20 @@
       <c r="B134" s="1">
         <v>100003</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C134" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D134" s="1">
         <v>8</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F134" s="1">
         <v>3</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3671,20 +3662,20 @@
       <c r="B135" s="1">
         <v>100003</v>
       </c>
-      <c r="C135" s="6" t="s">
+      <c r="C135" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D135" s="1">
         <v>8</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1">
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3694,20 +3685,20 @@
       <c r="B136" s="1">
         <v>100003</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D136" s="1">
         <v>8</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F136" s="1">
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3717,20 +3708,20 @@
       <c r="B137" s="1">
         <v>100003</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D137" s="1">
         <v>9</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1">
         <v>2</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3740,20 +3731,20 @@
       <c r="B138" s="1">
         <v>100003</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C138" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D138" s="1">
         <v>9</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F138" s="1">
         <v>3</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3763,20 +3754,20 @@
       <c r="B139" s="1">
         <v>100003</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C139" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D139" s="1">
         <v>9</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1">
         <v>1</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3786,20 +3777,20 @@
       <c r="B140" s="1">
         <v>100003</v>
       </c>
-      <c r="C140" s="6" t="s">
+      <c r="C140" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D140" s="1">
         <v>9</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F140" s="1">
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -3809,20 +3800,20 @@
       <c r="B141" s="1">
         <v>100003</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D141" s="1">
         <v>10</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1">
         <v>2</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -3832,20 +3823,20 @@
       <c r="B142" s="1">
         <v>100003</v>
       </c>
-      <c r="C142" s="6" t="s">
+      <c r="C142" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D142" s="1">
         <v>10</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F142" s="1">
         <v>3</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -3855,20 +3846,20 @@
       <c r="B143" s="1">
         <v>100003</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D143" s="1">
         <v>10</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1">
         <v>1</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -3878,20 +3869,20 @@
       <c r="B144" s="1">
         <v>100003</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D144" s="1">
         <v>10</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F144" s="1">
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -3901,20 +3892,20 @@
       <c r="B145" s="1">
         <v>100003</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>19</v>
+      <c r="C145" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D145" s="1">
         <v>11</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1">
         <v>2</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -3924,20 +3915,20 @@
       <c r="B146" s="1">
         <v>100003</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>19</v>
+      <c r="C146" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D146" s="1">
         <v>11</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F146" s="1">
         <v>3</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -3947,20 +3938,20 @@
       <c r="B147" s="1">
         <v>100003</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>19</v>
+      <c r="C147" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D147" s="1">
         <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1">
         <v>1</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -3970,20 +3961,20 @@
       <c r="B148" s="1">
         <v>100003</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>19</v>
+      <c r="C148" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D148" s="1">
         <v>11</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F148" s="1">
         <v>4</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -3993,20 +3984,20 @@
       <c r="B149" s="1">
         <v>100003</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>21</v>
+      <c r="C149" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D149" s="1">
         <v>12</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1">
         <v>2</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4016,20 +4007,20 @@
       <c r="B150" s="1">
         <v>100003</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>21</v>
+      <c r="C150" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D150" s="1">
         <v>12</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1">
         <v>3</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4039,20 +4030,20 @@
       <c r="B151" s="1">
         <v>100003</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>21</v>
+      <c r="C151" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D151" s="1">
         <v>12</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1">
         <v>1</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4062,20 +4053,20 @@
       <c r="B152" s="1">
         <v>100003</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>21</v>
+      <c r="C152" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D152" s="1">
         <v>12</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1">
         <v>4</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4085,20 +4076,20 @@
       <c r="B153" s="1">
         <v>100003</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>22</v>
+      <c r="C153" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D153" s="1">
         <v>13</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1">
         <v>2</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4108,20 +4099,20 @@
       <c r="B154" s="1">
         <v>100003</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>22</v>
+      <c r="C154" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D154" s="1">
         <v>13</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F154" s="1">
         <v>3</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4131,20 +4122,20 @@
       <c r="B155" s="1">
         <v>100003</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>22</v>
+      <c r="C155" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D155" s="1">
         <v>13</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1">
         <v>1</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4154,20 +4145,20 @@
       <c r="B156" s="1">
         <v>100003</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>22</v>
+      <c r="C156" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D156" s="1">
         <v>13</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F156" s="1">
         <v>4</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4177,20 +4168,20 @@
       <c r="B157" s="1">
         <v>100003</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>24</v>
+      <c r="C157" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D157" s="1">
         <v>14</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1">
         <v>2</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4200,20 +4191,20 @@
       <c r="B158" s="1">
         <v>100003</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>24</v>
+      <c r="C158" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D158" s="1">
         <v>14</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1">
         <v>3</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4223,20 +4214,20 @@
       <c r="B159" s="1">
         <v>100003</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>24</v>
+      <c r="C159" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D159" s="1">
         <v>14</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1">
         <v>1</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4246,24 +4237,24 @@
       <c r="B160" s="1">
         <v>100003</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>24</v>
+      <c r="C160" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D160" s="1">
         <v>14</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F160" s="1">
         <v>4</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:G144" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:G160" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
